--- a/artfynd/A 1960-2023 artfynd.xlsx
+++ b/artfynd/A 1960-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1960-2023 artfynd.xlsx
+++ b/artfynd/A 1960-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100952597</v>
+        <v>100952500</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541283.0533144015</v>
+        <v>541406</v>
       </c>
       <c r="R2" t="n">
-        <v>6383155.549160137</v>
+        <v>6383035</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-04-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100952570</v>
+        <v>100952607</v>
       </c>
       <c r="B3" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>2383</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541368.1955554446</v>
+        <v>541238</v>
       </c>
       <c r="R3" t="n">
-        <v>6383128.005128853</v>
+        <v>6383191</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2022-04-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100952592</v>
+        <v>100952570</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2779</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541403.9229567291</v>
+        <v>541368</v>
       </c>
       <c r="R4" t="n">
-        <v>6382995.423668789</v>
+        <v>6383128</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2022-04-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100952489</v>
+        <v>100952592</v>
       </c>
       <c r="B5" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541416.1832497454</v>
+        <v>541404</v>
       </c>
       <c r="R5" t="n">
-        <v>6383057.197635637</v>
+        <v>6382995</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1034,9 @@
           <t>2022-04-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100952500</v>
+        <v>100952520</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541406.2034821962</v>
+        <v>541372</v>
       </c>
       <c r="R6" t="n">
-        <v>6383035.116734635</v>
+        <v>6383127</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1131,9 @@
           <t>2022-04-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100952520</v>
+        <v>100952489</v>
       </c>
       <c r="B7" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541371.9658047195</v>
+        <v>541416</v>
       </c>
       <c r="R7" t="n">
-        <v>6383126.971445289</v>
+        <v>6383057</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1308,19 +1228,9 @@
           <t>2022-04-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,6 +1254,297 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100952513</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kuarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>541237</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6383198</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Pelarne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100952597</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kuarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>541283</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6383156</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Pelarne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100952598</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kuarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>541268</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6383143</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Pelarne</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1960-2023 artfynd.xlsx
+++ b/artfynd/A 1960-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100952500</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100952607</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100952570</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100952592</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100952520</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100952489</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100952513</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100952597</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,8 +1590,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100952598</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>